--- a/Result/14-12-24/HKEXstock_14-12-24period60RS90.xlsx
+++ b/Result/14-12-24/HKEXstock_14-12-24period60RS90.xlsx
@@ -1,15 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10917"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kelvinyue/Desktop/Coding project/StockAnalysis/Result/14-12-24/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB79922C-0871-3944-8A47-515C5AE22BA7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16080" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
@@ -277,12 +283,12 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="3">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="新細明體"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -290,8 +296,15 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="新細明體"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="新細明體"/>
+      <family val="2"/>
+      <charset val="136"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -337,17 +350,25 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="一般" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -385,7 +406,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -419,6 +440,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -453,9 +475,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -628,9 +651,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AO23"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14"/>
   <sheetData>
     <row r="1" spans="1:41">
       <c r="A1" s="1" t="s">
@@ -762,7 +785,7 @@
         <v>41</v>
       </c>
       <c r="B2">
-        <v>92.57164404223228</v>
+        <v>92.571644042232279</v>
       </c>
       <c r="C2">
         <v>31</v>
@@ -774,7 +797,7 @@
         <v>3.44</v>
       </c>
       <c r="F2">
-        <v>0.06239978363938713</v>
+        <v>6.2399783639387127E-2</v>
       </c>
       <c r="G2">
         <v>5.6</v>
@@ -789,16 +812,16 @@
         <v>3.454999983310699</v>
       </c>
       <c r="K2">
-        <v>3.358199992179871</v>
+        <v>3.3581999921798711</v>
       </c>
       <c r="L2">
-        <v>2.931899998188019</v>
+        <v>2.9318999981880189</v>
       </c>
       <c r="M2">
         <v>1.08</v>
       </c>
       <c r="N2">
-        <v>1.11</v>
+        <v>1.1100000000000001</v>
       </c>
       <c r="P2">
         <v>0</v>
@@ -825,7 +848,7 @@
         <v>0</v>
       </c>
       <c r="X2">
-        <v>2.01</v>
+        <v>2.0099999999999998</v>
       </c>
       <c r="Y2">
         <v>4.07</v>
@@ -843,7 +866,7 @@
         <v>64</v>
       </c>
       <c r="AD2">
-        <v>3.0150002</v>
+        <v>3.0150001999999998</v>
       </c>
       <c r="AE2" t="s">
         <v>64</v>
@@ -876,7 +899,7 @@
         <v>55.2</v>
       </c>
       <c r="AO2">
-        <v>82.09323929483207</v>
+        <v>82.093239294832074</v>
       </c>
     </row>
     <row r="3" spans="1:41">
@@ -884,7 +907,7 @@
         <v>42</v>
       </c>
       <c r="B3">
-        <v>90.53544494720965</v>
+        <v>90.535444947209655</v>
       </c>
       <c r="C3">
         <v>15</v>
@@ -893,34 +916,34 @@
         <v>31.35</v>
       </c>
       <c r="E3">
-        <v>2.18</v>
+        <v>2.1800000000000002</v>
       </c>
       <c r="F3">
-        <v>-0.447842694969406</v>
+        <v>-0.44784269496940599</v>
       </c>
       <c r="G3">
         <v>2.7</v>
       </c>
       <c r="H3">
-        <v>-0.5844797961236891</v>
+        <v>-0.58447979612368905</v>
       </c>
       <c r="I3">
-        <v>31.06000061035156</v>
+        <v>31.060000610351558</v>
       </c>
       <c r="J3">
         <v>29.13500003814697</v>
       </c>
       <c r="K3">
-        <v>27.18700004577637</v>
+        <v>27.187000045776369</v>
       </c>
       <c r="L3">
-        <v>19.68914999008179</v>
+        <v>19.689149990081791</v>
       </c>
       <c r="M3">
         <v>1.07</v>
       </c>
       <c r="N3">
-        <v>1.14</v>
+        <v>1.1399999999999999</v>
       </c>
       <c r="P3">
         <v>0</v>
@@ -935,7 +958,7 @@
         <v>8</v>
       </c>
       <c r="T3">
-        <v>14.44444444444444</v>
+        <v>14.444444444444439</v>
       </c>
       <c r="U3" t="b">
         <v>0</v>
@@ -965,7 +988,7 @@
         <v>64</v>
       </c>
       <c r="AD3">
-        <v>11.476</v>
+        <v>11.476000000000001</v>
       </c>
       <c r="AE3" t="s">
         <v>64</v>
@@ -989,7 +1012,7 @@
         <v>0.89</v>
       </c>
       <c r="AL3">
-        <v>1.13</v>
+        <v>1.1299999999999999</v>
       </c>
       <c r="AM3">
         <v>26.97</v>
@@ -998,7 +1021,7 @@
         <v>38.9</v>
       </c>
       <c r="AO3">
-        <v>78.64700444361125</v>
+        <v>78.647004443611252</v>
       </c>
     </row>
     <row r="4" spans="1:41">
@@ -1006,7 +1029,7 @@
         <v>43</v>
       </c>
       <c r="B4">
-        <v>87.25490196078431</v>
+        <v>87.254901960784309</v>
       </c>
       <c r="C4">
         <v>159</v>
@@ -1018,7 +1041,7 @@
         <v>1.63</v>
       </c>
       <c r="F4">
-        <v>-0.6705675864256254</v>
+        <v>-0.67056758642562542</v>
       </c>
       <c r="G4">
         <v>4.21</v>
@@ -1027,13 +1050,13 @@
         <v>-0.1445971765670748</v>
       </c>
       <c r="I4">
-        <v>5.646000003814697</v>
+        <v>5.6460000038146969</v>
       </c>
       <c r="J4">
-        <v>5.328500008583068</v>
+        <v>5.3285000085830676</v>
       </c>
       <c r="K4">
-        <v>5.263200006484985</v>
+        <v>5.2632000064849853</v>
       </c>
       <c r="L4">
         <v>5.114999997615814</v>
@@ -1117,10 +1140,10 @@
         <v>31.25</v>
       </c>
       <c r="AN4">
-        <v>4.399999999999999</v>
+        <v>4.3999999999999986</v>
       </c>
       <c r="AO4">
-        <v>74.52083503204435</v>
+        <v>74.520835032044346</v>
       </c>
     </row>
     <row r="5" spans="1:41">
@@ -1140,13 +1163,13 @@
         <v>2.65</v>
       </c>
       <c r="F5">
-        <v>-0.2575141513613642</v>
+        <v>-0.25751415136136419</v>
       </c>
       <c r="G5">
-        <v>4.14</v>
+        <v>4.1399999999999997</v>
       </c>
       <c r="H5">
-        <v>-0.1649890860829444</v>
+        <v>-0.16498908608294441</v>
       </c>
       <c r="I5">
         <v>15.66400012969971</v>
@@ -1155,16 +1178,16 @@
         <v>14.23300004005432</v>
       </c>
       <c r="K5">
-        <v>13.88959999084473</v>
+        <v>13.889599990844729</v>
       </c>
       <c r="L5">
-        <v>10.23450000762939</v>
+        <v>10.234500007629389</v>
       </c>
       <c r="M5">
-        <v>1.1</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="N5">
-        <v>1.13</v>
+        <v>1.1299999999999999</v>
       </c>
       <c r="O5" t="s">
         <v>63</v>
@@ -1182,7 +1205,7 @@
         <v>4</v>
       </c>
       <c r="T5">
-        <v>8.888888888888888</v>
+        <v>8.8888888888888875</v>
       </c>
       <c r="U5" t="b">
         <v>0</v>
@@ -1197,7 +1220,7 @@
         <v>7.24</v>
       </c>
       <c r="Y5">
-        <v>16.44</v>
+        <v>16.440000000000001</v>
       </c>
       <c r="Z5">
         <v>153.93</v>
@@ -1236,7 +1259,7 @@
         <v>1.5</v>
       </c>
       <c r="AL5">
-        <v>1.09</v>
+        <v>1.0900000000000001</v>
       </c>
       <c r="AM5">
         <v>-27.33</v>
@@ -1245,7 +1268,7 @@
         <v>954.8</v>
       </c>
       <c r="AO5">
-        <v>73.49392785436419</v>
+        <v>73.493927854364188</v>
       </c>
     </row>
     <row r="6" spans="1:41">
@@ -1253,7 +1276,7 @@
         <v>45</v>
       </c>
       <c r="B6">
-        <v>61.68929110105581</v>
+        <v>61.689291101055808</v>
       </c>
       <c r="C6">
         <v>12</v>
@@ -1265,25 +1288,25 @@
         <v>1.37</v>
       </c>
       <c r="F6">
-        <v>-0.7758557169322018</v>
+        <v>-0.77585571693220179</v>
       </c>
       <c r="G6">
         <v>1.99</v>
       </c>
       <c r="H6">
-        <v>-0.7913120212132229</v>
+        <v>-0.79131202121322286</v>
       </c>
       <c r="I6">
-        <v>4.142000007629394</v>
+        <v>4.1420000076293944</v>
       </c>
       <c r="J6">
-        <v>4.005000054836273</v>
+        <v>4.0050000548362732</v>
       </c>
       <c r="K6">
         <v>3.944000043869019</v>
       </c>
       <c r="L6">
-        <v>3.583350009918213</v>
+        <v>3.5833500099182132</v>
       </c>
       <c r="M6">
         <v>1.03</v>
@@ -1304,7 +1327,7 @@
         <v>0</v>
       </c>
       <c r="T6">
-        <v>8.333333333333332</v>
+        <v>8.3333333333333321</v>
       </c>
       <c r="U6" t="b">
         <v>0</v>
@@ -1364,10 +1387,10 @@
         <v>7.69</v>
       </c>
       <c r="AN6">
-        <v>5.899999999999999</v>
+        <v>5.8999999999999986</v>
       </c>
       <c r="AO6">
-        <v>62.06306558146051</v>
+        <v>62.063065581460513</v>
       </c>
     </row>
     <row r="7" spans="1:41">
@@ -1393,19 +1416,19 @@
         <v>4.26</v>
       </c>
       <c r="H7">
-        <v>-0.1300315269128824</v>
+        <v>-0.13003152691288239</v>
       </c>
       <c r="I7">
         <v>6.411999988555908</v>
       </c>
       <c r="J7">
-        <v>5.970999932289123</v>
+        <v>5.9709999322891232</v>
       </c>
       <c r="K7">
         <v>5.439399995803833</v>
       </c>
       <c r="L7">
-        <v>4.320949989557266</v>
+        <v>4.3209499895572661</v>
       </c>
       <c r="M7">
         <v>1.07</v>
@@ -1456,7 +1479,7 @@
         <v>64</v>
       </c>
       <c r="AD7">
-        <v>3.652</v>
+        <v>3.6520000000000001</v>
       </c>
       <c r="AE7" t="s">
         <v>64</v>
@@ -1477,7 +1500,7 @@
         <v>77</v>
       </c>
       <c r="AK7">
-        <v>0.07000000000000001</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="AL7">
         <v>0.4</v>
@@ -1489,7 +1512,7 @@
         <v>453.9</v>
       </c>
       <c r="AO7">
-        <v>60.05603639557634</v>
+        <v>60.056036395576342</v>
       </c>
     </row>
     <row r="8" spans="1:41">
@@ -1497,7 +1520,7 @@
         <v>47</v>
       </c>
       <c r="B8">
-        <v>71.22926093514329</v>
+        <v>71.229260935143287</v>
       </c>
       <c r="C8">
         <v>156</v>
@@ -1509,7 +1532,7 @@
         <v>0.92</v>
       </c>
       <c r="F8">
-        <v>-0.9580851735781994</v>
+        <v>-0.95808517357819944</v>
       </c>
       <c r="G8">
         <v>1.53</v>
@@ -1518,22 +1541,22 @@
         <v>-0.9253159980317941</v>
       </c>
       <c r="I8">
-        <v>9.710000038146973</v>
+        <v>9.7100000381469727</v>
       </c>
       <c r="J8">
-        <v>9.496499967575073</v>
+        <v>9.4964999675750725</v>
       </c>
       <c r="K8">
         <v>8.644799995422364</v>
       </c>
       <c r="L8">
-        <v>8.33090001821518</v>
+        <v>8.3309000182151802</v>
       </c>
       <c r="M8">
         <v>1.02</v>
       </c>
       <c r="N8">
-        <v>1.12</v>
+        <v>1.1200000000000001</v>
       </c>
       <c r="P8">
         <v>2</v>
@@ -1548,7 +1571,7 @@
         <v>1</v>
       </c>
       <c r="T8">
-        <v>7.222222222222221</v>
+        <v>7.2222222222222214</v>
       </c>
       <c r="U8" t="b">
         <v>1</v>
@@ -1602,7 +1625,7 @@
         <v>1.18</v>
       </c>
       <c r="AL8">
-        <v>1.16</v>
+        <v>1.1599999999999999</v>
       </c>
       <c r="AM8">
         <v>-1.69</v>
@@ -1611,7 +1634,7 @@
         <v>-15.3</v>
       </c>
       <c r="AO8">
-        <v>57.57253655789177</v>
+        <v>57.572536557891773</v>
       </c>
     </row>
     <row r="9" spans="1:41">
@@ -1619,7 +1642,7 @@
         <v>48</v>
       </c>
       <c r="B9">
-        <v>87.02865761689291</v>
+        <v>87.028657616892914</v>
       </c>
       <c r="C9">
         <v>21</v>
@@ -1631,7 +1654,7 @@
         <v>5.29</v>
       </c>
       <c r="F9">
-        <v>0.8115653276284884</v>
+        <v>0.81156532762848843</v>
       </c>
       <c r="G9">
         <v>5.26</v>
@@ -1640,7 +1663,7 @@
         <v>0.1612814661709682</v>
       </c>
       <c r="I9">
-        <v>3.138000011444092</v>
+        <v>3.1380000114440918</v>
       </c>
       <c r="J9">
         <v>3.030000007152557</v>
@@ -1655,7 +1678,7 @@
         <v>1.04</v>
       </c>
       <c r="N9">
-        <v>1.09</v>
+        <v>1.0900000000000001</v>
       </c>
       <c r="P9">
         <v>0</v>
@@ -1682,7 +1705,7 @@
         <v>0</v>
       </c>
       <c r="X9">
-        <v>2.07</v>
+        <v>2.0699999999999998</v>
       </c>
       <c r="Y9">
         <v>3.94</v>
@@ -1700,7 +1723,7 @@
         <v>64</v>
       </c>
       <c r="AD9">
-        <v>10.998</v>
+        <v>10.997999999999999</v>
       </c>
       <c r="AE9" t="s">
         <v>64</v>
@@ -1730,7 +1753,7 @@
         <v>80</v>
       </c>
       <c r="AN9">
-        <v>33.3</v>
+        <v>33.299999999999997</v>
       </c>
       <c r="AO9">
         <v>54.51484240055553</v>
@@ -1741,7 +1764,7 @@
         <v>49</v>
       </c>
       <c r="B10">
-        <v>94.00452488687783</v>
+        <v>94.004524886877832</v>
       </c>
       <c r="C10">
         <v>82</v>
@@ -1756,25 +1779,25 @@
         <v>-0.1076810425635439</v>
       </c>
       <c r="G10">
-        <v>4.56</v>
+        <v>4.5599999999999996</v>
       </c>
       <c r="H10">
-        <v>-0.04263762898772724</v>
+        <v>-4.2637628987727237E-2</v>
       </c>
       <c r="I10">
         <v>5.360000038146973</v>
       </c>
       <c r="J10">
-        <v>4.938000011444092</v>
+        <v>4.9380000114440916</v>
       </c>
       <c r="K10">
-        <v>4.491199998855591</v>
+        <v>4.4911999988555911</v>
       </c>
       <c r="L10">
         <v>3.945949999094009</v>
       </c>
       <c r="M10">
-        <v>1.09</v>
+        <v>1.0900000000000001</v>
       </c>
       <c r="N10">
         <v>1.19</v>
@@ -1810,7 +1833,7 @@
         <v>5.68</v>
       </c>
       <c r="Z10">
-        <v>150.23</v>
+        <v>150.22999999999999</v>
       </c>
       <c r="AA10" t="s">
         <v>64</v>
@@ -1822,7 +1845,7 @@
         <v>64</v>
       </c>
       <c r="AD10">
-        <v>-5.228</v>
+        <v>-5.2279999999999998</v>
       </c>
       <c r="AE10" t="s">
         <v>64</v>
@@ -1846,16 +1869,16 @@
         <v>-0.03</v>
       </c>
       <c r="AL10">
-        <v>0.29</v>
+        <v>0.28999999999999998</v>
       </c>
       <c r="AM10">
         <v>1066.67</v>
       </c>
       <c r="AN10">
-        <v>-2.3</v>
+        <v>-2.2999999999999998</v>
       </c>
       <c r="AO10">
-        <v>53.94211933128089</v>
+        <v>53.942119331280892</v>
       </c>
     </row>
     <row r="11" spans="1:41">
@@ -1863,7 +1886,7 @@
         <v>50</v>
       </c>
       <c r="B11">
-        <v>55.3921568627451</v>
+        <v>55.392156862745097</v>
       </c>
       <c r="C11">
         <v>94</v>
@@ -1875,25 +1898,25 @@
         <v>1.39</v>
       </c>
       <c r="F11">
-        <v>-0.7677566299701575</v>
+        <v>-0.76775662997015748</v>
       </c>
       <c r="G11">
         <v>1.71</v>
       </c>
       <c r="H11">
-        <v>-0.8728796592767011</v>
+        <v>-0.87287965927670108</v>
       </c>
       <c r="I11">
-        <v>6.439999961853028</v>
+        <v>6.4399999618530277</v>
       </c>
       <c r="J11">
-        <v>6.325499963760376</v>
+        <v>6.3254999637603762</v>
       </c>
       <c r="K11">
-        <v>6.226199989318848</v>
+        <v>6.2261999893188484</v>
       </c>
       <c r="L11">
-        <v>5.61334998846054</v>
+        <v>5.6133499884605396</v>
       </c>
       <c r="M11">
         <v>1.02</v>
@@ -1968,7 +1991,7 @@
         <v>0.72</v>
       </c>
       <c r="AL11">
-        <v>0.07000000000000001</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="AM11">
         <v>-90.28</v>
@@ -1985,7 +2008,7 @@
         <v>51</v>
       </c>
       <c r="B12">
-        <v>88.9894419306184</v>
+        <v>88.989441930618398</v>
       </c>
       <c r="C12">
         <v>142</v>
@@ -1997,25 +2020,25 @@
         <v>1.99</v>
       </c>
       <c r="F12">
-        <v>-0.5247840211088273</v>
+        <v>-0.52478402110882727</v>
       </c>
       <c r="G12">
         <v>3.73</v>
       </c>
       <c r="H12">
-        <v>-0.2844274132473231</v>
+        <v>-0.28442741324732312</v>
       </c>
       <c r="I12">
         <v>21.3</v>
       </c>
       <c r="J12">
-        <v>20.06800003051758</v>
+        <v>20.068000030517581</v>
       </c>
       <c r="K12">
         <v>19.89459995269775</v>
       </c>
       <c r="L12">
-        <v>18.48319996356964</v>
+        <v>18.483199963569639</v>
       </c>
       <c r="M12">
         <v>1.06</v>
@@ -2099,7 +2122,7 @@
         <v>209.1</v>
       </c>
       <c r="AO12">
-        <v>50.88861847894491</v>
+        <v>50.888618478944913</v>
       </c>
     </row>
     <row r="13" spans="1:41">
@@ -2107,7 +2130,7 @@
         <v>52</v>
       </c>
       <c r="B13">
-        <v>88.68778280542986</v>
+        <v>88.687782805429862</v>
       </c>
       <c r="C13">
         <v>237</v>
@@ -2116,25 +2139,25 @@
         <v>67.5</v>
       </c>
       <c r="E13">
-        <v>2.55</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="F13">
-        <v>-0.298009586171586</v>
+        <v>-0.29800958617158602</v>
       </c>
       <c r="G13">
         <v>4.04</v>
       </c>
       <c r="H13">
-        <v>-0.1941203853913294</v>
+        <v>-0.19412038539132939</v>
       </c>
       <c r="I13">
         <v>66.05</v>
       </c>
       <c r="J13">
-        <v>61.94000053405762</v>
+        <v>61.940000534057617</v>
       </c>
       <c r="K13">
-        <v>56.41000045776367</v>
+        <v>56.410000457763672</v>
       </c>
       <c r="L13">
         <v>48.36775016784668</v>
@@ -2170,7 +2193,7 @@
         <v>1</v>
       </c>
       <c r="X13">
-        <v>33.3</v>
+        <v>33.299999999999997</v>
       </c>
       <c r="Y13">
         <v>75.5</v>
@@ -2188,7 +2211,7 @@
         <v>64</v>
       </c>
       <c r="AD13">
-        <v>7.866000400000001</v>
+        <v>7.8660004000000008</v>
       </c>
       <c r="AE13" t="s">
         <v>64</v>
@@ -2215,13 +2238,13 @@
         <v>2.94</v>
       </c>
       <c r="AM13">
-        <v>71.93000000000001</v>
+        <v>71.930000000000007</v>
       </c>
       <c r="AN13">
         <v>147.1</v>
       </c>
       <c r="AO13">
-        <v>50.04095990619673</v>
+        <v>50.040959906196733</v>
       </c>
     </row>
     <row r="14" spans="1:41">
@@ -2229,7 +2252,7 @@
         <v>53</v>
       </c>
       <c r="B14">
-        <v>95.39969834087482</v>
+        <v>95.399698340874821</v>
       </c>
       <c r="C14">
         <v>87</v>
@@ -2247,22 +2270,22 @@
         <v>3.98</v>
       </c>
       <c r="H14">
-        <v>-0.2115991649763604</v>
+        <v>-0.21159916497636039</v>
       </c>
       <c r="I14">
         <v>1.724000024795532</v>
       </c>
       <c r="J14">
-        <v>1.574000000953674</v>
+        <v>1.5740000009536741</v>
       </c>
       <c r="K14">
         <v>1.337000000476837</v>
       </c>
       <c r="L14">
-        <v>1.121199997067451</v>
+        <v>1.1211999970674511</v>
       </c>
       <c r="M14">
-        <v>1.1</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="N14">
         <v>1.29</v>
@@ -2292,13 +2315,13 @@
         <v>1</v>
       </c>
       <c r="X14">
-        <v>0.5600000000000001</v>
+        <v>0.56000000000000005</v>
       </c>
       <c r="Y14">
         <v>1.8</v>
       </c>
       <c r="Z14">
-        <v>9.449999999999999</v>
+        <v>9.4499999999999993</v>
       </c>
       <c r="AA14" t="s">
         <v>64</v>
@@ -2310,7 +2333,7 @@
         <v>64</v>
       </c>
       <c r="AD14">
-        <v>3.715</v>
+        <v>3.7149999999999999</v>
       </c>
       <c r="AE14" t="s">
         <v>64</v>
@@ -2334,7 +2357,7 @@
         <v>0.05</v>
       </c>
       <c r="AL14">
-        <v>0.29</v>
+        <v>0.28999999999999998</v>
       </c>
       <c r="AM14">
         <v>480</v>
@@ -2343,7 +2366,7 @@
         <v>-27.3</v>
       </c>
       <c r="AO14">
-        <v>48.58570967162955</v>
+        <v>48.585709671629552</v>
       </c>
     </row>
     <row r="15" spans="1:41">
@@ -2351,7 +2374,7 @@
         <v>54</v>
       </c>
       <c r="B15">
-        <v>90.79939668174963</v>
+        <v>90.799396681749627</v>
       </c>
       <c r="C15">
         <v>176</v>
@@ -2363,28 +2386,28 @@
         <v>3.83</v>
       </c>
       <c r="F15">
-        <v>0.2203319793992518</v>
+        <v>0.22033197939925181</v>
       </c>
       <c r="G15">
         <v>4.55</v>
       </c>
       <c r="H15">
-        <v>-0.04555075891856569</v>
+        <v>-4.5550758918565692E-2</v>
       </c>
       <c r="I15">
-        <v>41.90999984741211</v>
+        <v>41.909999847412109</v>
       </c>
       <c r="J15">
-        <v>36.525</v>
+        <v>36.524999999999999</v>
       </c>
       <c r="K15">
-        <v>34.15899982452392</v>
+        <v>34.158999824523917</v>
       </c>
       <c r="L15">
-        <v>31.79774995803833</v>
+        <v>31.797749958038331</v>
       </c>
       <c r="M15">
-        <v>1.15</v>
+        <v>1.1499999999999999</v>
       </c>
       <c r="N15">
         <v>1.23</v>
@@ -2420,7 +2443,7 @@
         <v>43.3</v>
       </c>
       <c r="Z15">
-        <v>94.18000000000001</v>
+        <v>94.18</v>
       </c>
       <c r="AA15" t="s">
         <v>64</v>
@@ -2432,7 +2455,7 @@
         <v>64</v>
       </c>
       <c r="AD15">
-        <v>14.326</v>
+        <v>14.326000000000001</v>
       </c>
       <c r="AE15" t="s">
         <v>64</v>
@@ -2465,7 +2488,7 @@
         <v>0.1</v>
       </c>
       <c r="AO15">
-        <v>47.88965181260272</v>
+        <v>47.889651812602722</v>
       </c>
     </row>
     <row r="16" spans="1:41">
@@ -2473,7 +2496,7 @@
         <v>55</v>
       </c>
       <c r="B16">
-        <v>93.21266968325791</v>
+        <v>93.212669683257914</v>
       </c>
       <c r="C16">
         <v>102</v>
@@ -2482,31 +2505,31 @@
         <v>4.24</v>
       </c>
       <c r="E16">
-        <v>2.45</v>
+        <v>2.4500000000000002</v>
       </c>
       <c r="F16">
-        <v>-0.3385050209818075</v>
+        <v>-0.33850502098180751</v>
       </c>
       <c r="G16">
         <v>4.92</v>
       </c>
       <c r="H16">
-        <v>0.06223504852245904</v>
+        <v>6.2235048522459042E-2</v>
       </c>
       <c r="I16">
-        <v>4.239999866485595</v>
+        <v>4.2399998664855953</v>
       </c>
       <c r="J16">
-        <v>3.828499960899353</v>
+        <v>3.8284999608993528</v>
       </c>
       <c r="K16">
-        <v>3.482999987602234</v>
+        <v>3.4829999876022342</v>
       </c>
       <c r="L16">
-        <v>3.041199996471405</v>
+        <v>3.0411999964714052</v>
       </c>
       <c r="M16">
-        <v>1.11</v>
+        <v>1.1100000000000001</v>
       </c>
       <c r="N16">
         <v>1.22</v>
@@ -2554,7 +2577,7 @@
         <v>64</v>
       </c>
       <c r="AD16">
-        <v>-3.821</v>
+        <v>-3.8210000000000002</v>
       </c>
       <c r="AE16" t="s">
         <v>64</v>
@@ -2578,7 +2601,7 @@
         <v>-0.2</v>
       </c>
       <c r="AL16">
-        <v>0.29</v>
+        <v>0.28999999999999998</v>
       </c>
       <c r="AM16">
         <v>245</v>
@@ -2587,7 +2610,7 @@
         <v>-23.9</v>
       </c>
       <c r="AO16">
-        <v>46.41116998059053</v>
+        <v>46.411169980590529</v>
       </c>
     </row>
     <row r="17" spans="1:41">
@@ -2595,7 +2618,7 @@
         <v>56</v>
       </c>
       <c r="B17">
-        <v>98.79336349924586</v>
+        <v>98.793363499245856</v>
       </c>
       <c r="C17">
         <v>70</v>
@@ -2607,13 +2630,13 @@
         <v>5.15</v>
       </c>
       <c r="F17">
-        <v>0.7548717188941781</v>
+        <v>0.75487171889417815</v>
       </c>
       <c r="G17">
         <v>13.81</v>
       </c>
       <c r="H17">
-        <v>2.652007557037891</v>
+        <v>2.6520075570378912</v>
       </c>
       <c r="I17">
         <v>16.67599983215332</v>
@@ -2622,16 +2645,16 @@
         <v>15.21599998474121</v>
       </c>
       <c r="K17">
-        <v>14.91899995803833</v>
+        <v>14.918999958038331</v>
       </c>
       <c r="L17">
-        <v>8.529650008678436</v>
+        <v>8.5296500086784359</v>
       </c>
       <c r="M17">
-        <v>1.1</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="N17">
-        <v>1.12</v>
+        <v>1.1200000000000001</v>
       </c>
       <c r="P17">
         <v>0</v>
@@ -2676,7 +2699,7 @@
         <v>64</v>
       </c>
       <c r="AD17">
-        <v>7.7470005</v>
+        <v>7.7470005000000004</v>
       </c>
       <c r="AE17" t="s">
         <v>64</v>
@@ -2697,7 +2720,7 @@
         <v>82</v>
       </c>
       <c r="AK17">
-        <v>1.09</v>
+        <v>1.0900000000000001</v>
       </c>
       <c r="AL17">
         <v>1.31</v>
@@ -2709,7 +2732,7 @@
         <v>43.4</v>
       </c>
       <c r="AO17">
-        <v>45.2201072307214</v>
+        <v>45.220107230721403</v>
       </c>
     </row>
     <row r="18" spans="1:41">
@@ -2717,7 +2740,7 @@
         <v>57</v>
       </c>
       <c r="B18">
-        <v>97.20965309200604</v>
+        <v>97.209653092006036</v>
       </c>
       <c r="C18">
         <v>30</v>
@@ -2729,28 +2752,28 @@
         <v>7.04</v>
       </c>
       <c r="F18">
-        <v>1.520235436807368</v>
+        <v>1.5202354368073681</v>
       </c>
       <c r="G18">
         <v>5.81</v>
       </c>
       <c r="H18">
-        <v>0.3215036123670859</v>
+        <v>0.32150361236708591</v>
       </c>
       <c r="I18">
-        <v>4.12000002861023</v>
+        <v>4.1200000286102298</v>
       </c>
       <c r="J18">
         <v>3.767000019550323</v>
       </c>
       <c r="K18">
-        <v>3.072800011634827</v>
+        <v>3.0728000116348269</v>
       </c>
       <c r="L18">
         <v>2.705849996805191</v>
       </c>
       <c r="M18">
-        <v>1.09</v>
+        <v>1.0900000000000001</v>
       </c>
       <c r="N18">
         <v>1.34</v>
@@ -2798,7 +2821,7 @@
         <v>64</v>
       </c>
       <c r="AD18">
-        <v>-4.3390002</v>
+        <v>-4.3390002000000001</v>
       </c>
       <c r="AE18" t="s">
         <v>64</v>
@@ -2819,7 +2842,7 @@
         <v>75</v>
       </c>
       <c r="AK18">
-        <v>-0.58</v>
+        <v>-0.57999999999999996</v>
       </c>
       <c r="AL18">
         <v>0.11</v>
@@ -2831,7 +2854,7 @@
         <v>-47.9</v>
       </c>
       <c r="AO18">
-        <v>45.00718684968844</v>
+        <v>45.007186849688438</v>
       </c>
     </row>
     <row r="19" spans="1:41">
@@ -2839,7 +2862,7 @@
         <v>58</v>
       </c>
       <c r="B19">
-        <v>81.41025641025641</v>
+        <v>81.410256410256409</v>
       </c>
       <c r="C19">
         <v>191</v>
@@ -2851,22 +2874,22 @@
         <v>3.09</v>
       </c>
       <c r="F19">
-        <v>-0.07933423819638881</v>
+        <v>-7.9334238196388809E-2</v>
       </c>
       <c r="G19">
         <v>3.7</v>
       </c>
       <c r="H19">
-        <v>-0.2931668030398386</v>
+        <v>-0.29316680303983861</v>
       </c>
       <c r="I19">
         <v>2.386000013351441</v>
       </c>
       <c r="J19">
-        <v>2.329499995708466</v>
+        <v>2.3294999957084661</v>
       </c>
       <c r="K19">
-        <v>2.215599999427795</v>
+        <v>2.2155999994277948</v>
       </c>
       <c r="L19">
         <v>2.168650002479553</v>
@@ -2941,7 +2964,7 @@
         <v>75</v>
       </c>
       <c r="AK19">
-        <v>0.29</v>
+        <v>0.28999999999999998</v>
       </c>
       <c r="AL19">
         <v>0.41</v>
@@ -2950,10 +2973,10 @@
         <v>41.38</v>
       </c>
       <c r="AN19">
-        <v>-4.100000000000001</v>
+        <v>-4.1000000000000014</v>
       </c>
       <c r="AO19">
-        <v>43.58433651982806</v>
+        <v>43.584336519828057</v>
       </c>
     </row>
     <row r="20" spans="1:41">
@@ -2961,7 +2984,7 @@
         <v>59</v>
       </c>
       <c r="B20">
-        <v>53.69532428355958</v>
+        <v>53.695324283559579</v>
       </c>
       <c r="C20">
         <v>58</v>
@@ -2973,25 +2996,25 @@
         <v>0.91</v>
       </c>
       <c r="F20">
-        <v>-0.9621347170592215</v>
+        <v>-0.96213471705922149</v>
       </c>
       <c r="G20">
         <v>1.83</v>
       </c>
       <c r="H20">
-        <v>-0.837922100106639</v>
+        <v>-0.83792210010663903</v>
       </c>
       <c r="I20">
-        <v>4.703999996185303</v>
+        <v>4.7039999961853027</v>
       </c>
       <c r="J20">
         <v>4.5625</v>
       </c>
       <c r="K20">
-        <v>4.561599979400635</v>
+        <v>4.5615999794006354</v>
       </c>
       <c r="L20">
-        <v>4.449650014638901</v>
+        <v>4.4496500146389009</v>
       </c>
       <c r="M20">
         <v>1.03</v>
@@ -3075,7 +3098,7 @@
         <v>7.8</v>
       </c>
       <c r="AO20">
-        <v>43.21357146800179</v>
+        <v>43.213571468001788</v>
       </c>
     </row>
     <row r="21" spans="1:41">
@@ -3083,7 +3106,7 @@
         <v>60</v>
       </c>
       <c r="B21">
-        <v>43.36349924585219</v>
+        <v>43.363499245852189</v>
       </c>
       <c r="C21">
         <v>151</v>
@@ -3095,25 +3118,25 @@
         <v>0.62</v>
       </c>
       <c r="F21">
-        <v>-1.079571478008864</v>
+        <v>-1.0795714780088641</v>
       </c>
       <c r="G21">
         <v>1.38</v>
       </c>
       <c r="H21">
-        <v>-0.9690129469943718</v>
+        <v>-0.96901294699437179</v>
       </c>
       <c r="I21">
-        <v>74.10000152587891</v>
+        <v>74.100001525878909</v>
       </c>
       <c r="J21">
-        <v>72.27000045776367</v>
+        <v>72.270000457763672</v>
       </c>
       <c r="K21">
-        <v>72.26799987792968</v>
+        <v>72.267999877929682</v>
       </c>
       <c r="L21">
-        <v>72.08399990081787</v>
+        <v>72.083999900817872</v>
       </c>
       <c r="M21">
         <v>1.03</v>
@@ -3164,7 +3187,7 @@
         <v>64</v>
       </c>
       <c r="AD21">
-        <v>10.508</v>
+        <v>10.507999999999999</v>
       </c>
       <c r="AE21" t="s">
         <v>64</v>
@@ -3194,10 +3217,10 @@
         <v>7.33</v>
       </c>
       <c r="AN21">
-        <v>4.6</v>
+        <v>4.5999999999999996</v>
       </c>
       <c r="AO21">
-        <v>42.73743222156724</v>
+        <v>42.737432221567239</v>
       </c>
     </row>
     <row r="22" spans="1:41">
@@ -3205,13 +3228,13 @@
         <v>61</v>
       </c>
       <c r="B22">
-        <v>99.81146304675717</v>
+        <v>99.811463046757169</v>
       </c>
       <c r="C22">
         <v>37</v>
       </c>
       <c r="D22">
-        <v>10.12</v>
+        <v>10.119999999999999</v>
       </c>
       <c r="E22">
         <v>11.75</v>
@@ -3226,22 +3249,22 @@
         <v>3.036540707908574</v>
       </c>
       <c r="I22">
-        <v>9.705999946594238</v>
+        <v>9.7059999465942379</v>
       </c>
       <c r="J22">
-        <v>8.433000040054321</v>
+        <v>8.4330000400543206</v>
       </c>
       <c r="K22">
-        <v>4.83960001707077</v>
+        <v>4.8396000170707696</v>
       </c>
       <c r="L22">
-        <v>3.039550002217293</v>
+        <v>3.0395500022172932</v>
       </c>
       <c r="M22">
-        <v>1.15</v>
+        <v>1.1499999999999999</v>
       </c>
       <c r="N22">
-        <v>2.01</v>
+        <v>2.0099999999999998</v>
       </c>
       <c r="P22">
         <v>0</v>
@@ -3268,7 +3291,7 @@
         <v>0</v>
       </c>
       <c r="X22">
-        <v>1.13</v>
+        <v>1.1299999999999999</v>
       </c>
       <c r="Y22">
         <v>11.28</v>
@@ -3286,7 +3309,7 @@
         <v>64</v>
       </c>
       <c r="AD22">
-        <v>7.029000000000001</v>
+        <v>7.0290000000000008</v>
       </c>
       <c r="AE22" t="s">
         <v>64</v>
@@ -3319,7 +3342,7 @@
         <v>-74.2</v>
       </c>
       <c r="AO22">
-        <v>36.58269298421221</v>
+        <v>36.582692984212208</v>
       </c>
     </row>
     <row r="23" spans="1:41">
@@ -3327,7 +3350,7 @@
         <v>62</v>
       </c>
       <c r="B23">
-        <v>93.58974358974359</v>
+        <v>93.589743589743591</v>
       </c>
       <c r="C23">
         <v>211</v>
@@ -3336,31 +3359,31 @@
         <v>2.35</v>
       </c>
       <c r="E23">
-        <v>4.44</v>
+        <v>4.4400000000000004</v>
       </c>
       <c r="F23">
-        <v>0.4673541317416042</v>
+        <v>0.46735413174160417</v>
       </c>
       <c r="G23">
         <v>4.7</v>
       </c>
       <c r="H23">
-        <v>-0.001853809955988006</v>
+        <v>-1.8538099559880061E-3</v>
       </c>
       <c r="I23">
-        <v>2.3</v>
+        <v>2.2999999999999998</v>
       </c>
       <c r="J23">
-        <v>2.052499985694885</v>
+        <v>2.0524999856948849</v>
       </c>
       <c r="K23">
-        <v>1.848199992179871</v>
+        <v>1.8481999921798711</v>
       </c>
       <c r="L23">
-        <v>1.845699995756149</v>
+        <v>1.8456999957561491</v>
       </c>
       <c r="M23">
-        <v>1.12</v>
+        <v>1.1200000000000001</v>
       </c>
       <c r="N23">
         <v>1.24</v>
@@ -3408,7 +3431,7 @@
         <v>64</v>
       </c>
       <c r="AD23">
-        <v>1.824</v>
+        <v>1.8240000000000001</v>
       </c>
       <c r="AE23" t="s">
         <v>64</v>
@@ -3438,13 +3461,14 @@
         <v>46.67</v>
       </c>
       <c r="AN23">
-        <v>-72.59999999999999</v>
+        <v>-72.599999999999994</v>
       </c>
       <c r="AO23">
-        <v>31.71776616257836</v>
+        <v>31.717766162578361</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>